--- a/venue-access/data/raw/NI2024PopulationData.xlsx
+++ b/venue-access/data/raw/NI2024PopulationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emitr\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22877DDE-2446-49EA-B299-67B736B0891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE29FA-6382-4BD4-A20B-E2BB557027CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF6D9B56-AAF7-4E5E-ABCC-E064BAD438E6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="3781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="3782">
   <si>
     <t>N20000001</t>
   </si>
@@ -11382,6 +11382,9 @@
   </si>
   <si>
     <t>DZ_CODE</t>
+  </si>
+  <si>
+    <t>Population</t>
   </si>
 </sst>
 </file>
@@ -11718,8 +11721,8 @@
       <c r="A1" s="1" t="s">
         <v>3780</v>
       </c>
-      <c r="B1" s="1">
-        <v>2024</v>
+      <c r="B1" s="1" t="s">
+        <v>3781</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -41977,12 +41980,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039A21D2C572FAA49A6063FC06EDE7565" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="21749a8e5f24a2895fa123a1cc634466">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6dae40ac-40d2-474a-a8e4-2d4367ce5ac2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60e4fd1678cb5c77ca2c414f37809603" ns3:_="">
     <xsd:import namespace="6dae40ac-40d2-474a-a8e4-2d4367ce5ac2"/>
@@ -42126,6 +42123,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC319920-BD78-450E-921A-F4F3CE02D901}">
   <ds:schemaRefs>
@@ -42135,22 +42138,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC78E24-0820-4C48-A68E-B39DBDC85C13}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="6dae40ac-40d2-474a-a8e4-2d4367ce5ac2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B75D28C-00DC-42BC-8471-C189EE6F0A56}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42166,4 +42153,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC78E24-0820-4C48-A68E-B39DBDC85C13}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6dae40ac-40d2-474a-a8e4-2d4367ce5ac2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>